--- a/pages/WR_progressions/Women_TS.xlsx
+++ b/pages/WR_progressions/Women_TS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\WR progressions\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A6688A-7C06-4C50-836F-1A2D2F5C13F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC1F15B-3D9F-4745-B01B-84C6D5F108BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{7C46F054-B1D4-4CFB-8B8C-DD123752A474}"/>
   </bookViews>

--- a/pages/WR_progressions/Women_TS.xlsx
+++ b/pages/WR_progressions/Women_TS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\WR_progressions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAC1F15B-3D9F-4745-B01B-84C6D5F108BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8538802C-0332-4CD4-B7F3-1E8FA5335620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{7C46F054-B1D4-4CFB-8B8C-DD123752A474}"/>
   </bookViews>
@@ -83,10 +83,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,8 +571,76 @@
       </c>
       <c r="J10" s="1"/>
     </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>45.472000000000001</v>
+      </c>
+      <c r="B11">
+        <v>45.472000000000001</v>
+      </c>
+      <c r="C11" s="2">
+        <v>45509</v>
+      </c>
+      <c r="D11" s="3">
+        <v>45509</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>45.377000000000002</v>
+      </c>
+      <c r="B12">
+        <v>45.377000000000002</v>
+      </c>
+      <c r="C12" s="2">
+        <v>45509</v>
+      </c>
+      <c r="D12" s="3">
+        <v>45509</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>45.347999999999999</v>
+      </c>
+      <c r="B13">
+        <v>45.347999999999999</v>
+      </c>
+      <c r="C13" s="2">
+        <v>45509</v>
+      </c>
+      <c r="D13" s="3">
+        <v>45509</v>
+      </c>
+    </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>45.338000000000001</v>
+      </c>
+      <c r="B14">
+        <v>45.338000000000001</v>
+      </c>
+      <c r="C14" s="2">
+        <v>45509</v>
+      </c>
+      <c r="D14" s="3">
+        <v>45509</v>
+      </c>
       <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>45.186</v>
+      </c>
+      <c r="B15">
+        <v>45.186</v>
+      </c>
+      <c r="C15" s="2">
+        <v>45509</v>
+      </c>
+      <c r="D15" s="3">
+        <v>45509</v>
+      </c>
     </row>
     <row r="18" spans="10:10" x14ac:dyDescent="0.45">
       <c r="J18" s="1"/>
